--- a/artfynd/A 8524-2026 artfynd.xlsx
+++ b/artfynd/A 8524-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132439658</v>
+        <v>132439666</v>
       </c>
       <c r="B2" t="n">
-        <v>79952</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551225</v>
+        <v>551243</v>
       </c>
       <c r="R2" t="n">
-        <v>6709574</v>
+        <v>6709718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132439610</v>
+        <v>132439649</v>
       </c>
       <c r="B3" t="n">
-        <v>93206</v>
+        <v>89354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550990</v>
+        <v>551231</v>
       </c>
       <c r="R3" t="n">
-        <v>6709446</v>
+        <v>6709504</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132439669</v>
+        <v>132439665</v>
       </c>
       <c r="B4" t="n">
-        <v>93206</v>
+        <v>81355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551233</v>
+        <v>551263</v>
       </c>
       <c r="R4" t="n">
-        <v>6709720</v>
+        <v>6709683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132439660</v>
+        <v>132439680</v>
       </c>
       <c r="B5" t="n">
-        <v>79952</v>
+        <v>92027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551265</v>
+        <v>551264</v>
       </c>
       <c r="R5" t="n">
-        <v>6709641</v>
+        <v>6709746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132439608</v>
+        <v>132439607</v>
       </c>
       <c r="B6" t="n">
-        <v>79952</v>
+        <v>92188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>3008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551023</v>
+        <v>551082</v>
       </c>
       <c r="R6" t="n">
-        <v>6709441</v>
+        <v>6709484</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132439665</v>
+        <v>132439685</v>
       </c>
       <c r="B7" t="n">
-        <v>81318</v>
+        <v>92188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>3008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551263</v>
+        <v>551331</v>
       </c>
       <c r="R7" t="n">
-        <v>6709683</v>
+        <v>6709718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132439616</v>
+        <v>132439641</v>
       </c>
       <c r="B8" t="n">
-        <v>97995</v>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>3382</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Aspskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Conferticium ravum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Burt) Ginns &amp; G.W. Freeman</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551158</v>
+        <v>551064</v>
       </c>
       <c r="R8" t="n">
-        <v>6709205</v>
+        <v>6709402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,22 +1382,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I håligheter på stående, levande asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132439680</v>
+        <v>132439609</v>
       </c>
       <c r="B9" t="n">
-        <v>91971</v>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,34 +1440,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551264</v>
+        <v>550993</v>
       </c>
       <c r="R9" t="n">
-        <v>6709746</v>
+        <v>6709449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,22 +1503,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,45 +1545,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132439621</v>
+        <v>132439610</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>93271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551212</v>
+        <v>550990</v>
       </c>
       <c r="R10" t="n">
-        <v>6709140</v>
+        <v>6709446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1629,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,42 +1661,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132439627</v>
+        <v>132439611</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>93271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1700,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551369</v>
+        <v>550946</v>
       </c>
       <c r="R11" t="n">
-        <v>6709297</v>
+        <v>6709448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,22 +1735,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,42 +1777,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132439653</v>
+        <v>132439632</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>93271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1816,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551344</v>
+        <v>551181</v>
       </c>
       <c r="R12" t="n">
-        <v>6709420</v>
+        <v>6709317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1888,14 +1893,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132439640</v>
+        <v>132439635</v>
       </c>
       <c r="B13" t="n">
-        <v>93206</v>
+        <v>93271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1932,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551073</v>
+        <v>551180</v>
       </c>
       <c r="R13" t="n">
-        <v>6709409</v>
+        <v>6709375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,47 +2009,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132439620</v>
+        <v>132439636</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>93271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551210</v>
+        <v>551149</v>
       </c>
       <c r="R14" t="n">
-        <v>6709145</v>
+        <v>6709397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132439659</v>
+        <v>132439637</v>
       </c>
       <c r="B15" t="n">
-        <v>79952</v>
+        <v>93271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,34 +2136,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551258</v>
+        <v>551137</v>
       </c>
       <c r="R15" t="n">
-        <v>6709615</v>
+        <v>6709401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2205,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132439672</v>
+        <v>132439640</v>
       </c>
       <c r="B16" t="n">
-        <v>79952</v>
+        <v>93271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,34 +2252,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551172</v>
+        <v>551073</v>
       </c>
       <c r="R16" t="n">
-        <v>6709733</v>
+        <v>6709409</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,14 +2357,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132439636</v>
+        <v>132439669</v>
       </c>
       <c r="B17" t="n">
-        <v>93206</v>
+        <v>93271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2383,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551149</v>
+        <v>551233</v>
       </c>
       <c r="R17" t="n">
-        <v>6709397</v>
+        <v>6709720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,7 +2446,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,32 +2473,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132439663</v>
+        <v>132439621</v>
       </c>
       <c r="B18" t="n">
-        <v>79952</v>
+        <v>91937</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2490,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551254</v>
+        <v>551212</v>
       </c>
       <c r="R18" t="n">
-        <v>6709678</v>
+        <v>6709140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2520,22 +2538,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,50 +2580,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132439652</v>
+        <v>132439606</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551308</v>
+        <v>551183</v>
       </c>
       <c r="R19" t="n">
-        <v>6709413</v>
+        <v>6709426</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,22 +2645,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,54 +2687,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132439657</v>
+        <v>132439608</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>79992</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551260</v>
+        <v>551023</v>
       </c>
       <c r="R20" t="n">
-        <v>6709510</v>
+        <v>6709441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,22 +2752,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,50 +2794,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132439662</v>
+        <v>132439633</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551280</v>
+        <v>551164</v>
       </c>
       <c r="R21" t="n">
-        <v>6709660</v>
+        <v>6709397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,7 +2864,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2875,7 +2874,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132439649</v>
+        <v>132439639</v>
       </c>
       <c r="B22" t="n">
-        <v>89300</v>
+        <v>79992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,21 +2912,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551231</v>
+        <v>551072</v>
       </c>
       <c r="R22" t="n">
-        <v>6709504</v>
+        <v>6709406</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2972,7 +2971,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2982,7 +2981,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,54 +3008,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132439635</v>
+        <v>132439642</v>
       </c>
       <c r="B23" t="n">
-        <v>93206</v>
+        <v>79992</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551180</v>
+        <v>551067</v>
       </c>
       <c r="R23" t="n">
-        <v>6709375</v>
+        <v>6709418</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3088,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3098,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,50 +3115,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132439634</v>
+        <v>132439643</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>551168</v>
+        <v>551064</v>
       </c>
       <c r="R24" t="n">
-        <v>6709397</v>
+        <v>6709434</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3200,7 +3185,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3210,7 +3195,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,54 +3222,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132439617</v>
+        <v>132439644</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79992</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>551151</v>
+        <v>551030</v>
       </c>
       <c r="R25" t="n">
-        <v>6709201</v>
+        <v>6709594</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3311,22 +3287,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3353,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132439633</v>
+        <v>132439646</v>
       </c>
       <c r="B26" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,10 +3364,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>551164</v>
+        <v>551019</v>
       </c>
       <c r="R26" t="n">
-        <v>6709397</v>
+        <v>6709636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,7 +3399,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3409,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,7 +3439,7 @@
         <v>132439648</v>
       </c>
       <c r="B27" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,10 +3543,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132439681</v>
+        <v>132439658</v>
       </c>
       <c r="B28" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,10 +3578,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>551270</v>
+        <v>551225</v>
       </c>
       <c r="R28" t="n">
-        <v>6709734</v>
+        <v>6709574</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3637,7 +3613,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3647,7 +3623,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3674,54 +3650,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132439626</v>
+        <v>132439659</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>551368</v>
+        <v>551258</v>
       </c>
       <c r="R29" t="n">
-        <v>6709309</v>
+        <v>6709615</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3763,7 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3790,50 +3757,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132445767</v>
+        <v>132439660</v>
       </c>
       <c r="B30" t="n">
-        <v>57145</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>551127</v>
+        <v>551265</v>
       </c>
       <c r="R30" t="n">
-        <v>6709733</v>
+        <v>6709641</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3827,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3837,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,54 +3864,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132439654</v>
+        <v>132439663</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>551317</v>
+        <v>551254</v>
       </c>
       <c r="R31" t="n">
-        <v>6709485</v>
+        <v>6709678</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,7 +3934,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3991,7 +3944,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4018,54 +3971,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132439632</v>
+        <v>132439664</v>
       </c>
       <c r="B32" t="n">
-        <v>93206</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>551181</v>
+        <v>551262</v>
       </c>
       <c r="R32" t="n">
-        <v>6709317</v>
+        <v>6709678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4097,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4107,7 +4051,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På grov, kolad stubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4134,50 +4083,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132439673</v>
+        <v>132439667</v>
       </c>
       <c r="B33" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>551162</v>
+        <v>551243</v>
       </c>
       <c r="R33" t="n">
-        <v>6709731</v>
+        <v>6709717</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4209,7 +4153,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4219,7 +4163,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4246,54 +4190,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132439650</v>
+        <v>132439670</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>551247</v>
+        <v>551217</v>
       </c>
       <c r="R34" t="n">
-        <v>6709492</v>
+        <v>6709702</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,7 +4260,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4335,7 +4270,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4362,10 +4297,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132439683</v>
+        <v>132439671</v>
       </c>
       <c r="B35" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4397,10 +4332,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>551277</v>
+        <v>551165</v>
       </c>
       <c r="R35" t="n">
-        <v>6709733</v>
+        <v>6709727</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,7 +4367,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4442,7 +4377,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,54 +4404,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132439628</v>
+        <v>132439672</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>551318</v>
+        <v>551172</v>
       </c>
       <c r="R36" t="n">
-        <v>6709291</v>
+        <v>6709733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4548,7 +4474,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4558,7 +4484,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,10 +4511,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132439682</v>
+        <v>132439679</v>
       </c>
       <c r="B37" t="n">
-        <v>79952</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4620,10 +4546,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>551271</v>
+        <v>551266</v>
       </c>
       <c r="R37" t="n">
-        <v>6709738</v>
+        <v>6709746</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4655,7 +4581,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4665,7 +4591,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4692,10 +4618,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132439605</v>
+        <v>132439681</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,39 +4629,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>551188</v>
+        <v>551270</v>
       </c>
       <c r="R38" t="n">
-        <v>6709399</v>
+        <v>6709734</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4762,22 +4683,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4804,54 +4725,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132439613</v>
+        <v>132439682</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>79992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550915</v>
+        <v>551271</v>
       </c>
       <c r="R39" t="n">
-        <v>6709323</v>
+        <v>6709738</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4878,22 +4790,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4920,50 +4832,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132439761</v>
+        <v>132439683</v>
       </c>
       <c r="B40" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551427</v>
+        <v>551277</v>
       </c>
       <c r="R40" t="n">
-        <v>6709469</v>
+        <v>6709733</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4995,7 +4902,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5005,7 +4912,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5032,10 +4939,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132439661</v>
+        <v>132439684</v>
       </c>
       <c r="B41" t="n">
-        <v>57955</v>
+        <v>79992</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5043,39 +4950,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551278</v>
+        <v>551325</v>
       </c>
       <c r="R41" t="n">
-        <v>6709661</v>
+        <v>6709728</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5107,7 +5009,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5117,7 +5019,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5144,54 +5046,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132439637</v>
+        <v>132439738</v>
       </c>
       <c r="B42" t="n">
-        <v>93206</v>
+        <v>79992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551137</v>
+        <v>551356</v>
       </c>
       <c r="R42" t="n">
-        <v>6709401</v>
+        <v>6709642</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,7 +5116,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5233,7 +5126,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5260,42 +5153,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132439656</v>
+        <v>132439605</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>57972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5304,10 +5193,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551280</v>
+        <v>551188</v>
       </c>
       <c r="R43" t="n">
-        <v>6709513</v>
+        <v>6709399</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5334,22 +5223,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5376,45 +5265,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132439671</v>
+        <v>132439661</v>
       </c>
       <c r="B44" t="n">
-        <v>79952</v>
+        <v>57972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551165</v>
+        <v>551278</v>
       </c>
       <c r="R44" t="n">
-        <v>6709727</v>
+        <v>6709661</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5446,7 +5340,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5456,7 +5350,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5483,45 +5377,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132439646</v>
+        <v>132439675</v>
       </c>
       <c r="B45" t="n">
-        <v>79952</v>
+        <v>57972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551019</v>
+        <v>551096</v>
       </c>
       <c r="R45" t="n">
-        <v>6709636</v>
+        <v>6709777</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5553,7 +5452,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5563,7 +5462,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5590,45 +5489,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132439666</v>
+        <v>132439677</v>
       </c>
       <c r="B46" t="n">
-        <v>78999</v>
+        <v>57972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551243</v>
+        <v>551147</v>
       </c>
       <c r="R46" t="n">
-        <v>6709718</v>
+        <v>6709859</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5660,7 +5564,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5670,7 +5574,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>I äldre asp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5697,45 +5606,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132439642</v>
+        <v>132445767</v>
       </c>
       <c r="B47" t="n">
-        <v>79952</v>
+        <v>57162</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551067</v>
+        <v>551127</v>
       </c>
       <c r="R47" t="n">
-        <v>6709418</v>
+        <v>6709733</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5767,7 +5681,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5777,7 +5691,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5804,10 +5718,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132439667</v>
+        <v>132439647</v>
       </c>
       <c r="B48" t="n">
-        <v>79952</v>
+        <v>58136</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5815,34 +5729,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551243</v>
+        <v>551023</v>
       </c>
       <c r="R48" t="n">
-        <v>6709717</v>
+        <v>6709628</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5874,7 +5793,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5884,7 +5803,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5911,45 +5830,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132439639</v>
+        <v>132439634</v>
       </c>
       <c r="B49" t="n">
-        <v>79952</v>
+        <v>8460</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>551072</v>
+        <v>551168</v>
       </c>
       <c r="R49" t="n">
-        <v>6709406</v>
+        <v>6709397</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5981,7 +5905,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5991,7 +5915,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6018,45 +5942,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132439664</v>
+        <v>132439652</v>
       </c>
       <c r="B50" t="n">
-        <v>79952</v>
+        <v>8460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>551262</v>
+        <v>551308</v>
       </c>
       <c r="R50" t="n">
-        <v>6709678</v>
+        <v>6709413</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6088,7 +6017,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6098,12 +6027,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På grov, kolad stubbe</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6130,38 +6054,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132439647</v>
+        <v>132439662</v>
       </c>
       <c r="B51" t="n">
-        <v>58119</v>
+        <v>8460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6170,10 +6094,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>551023</v>
+        <v>551280</v>
       </c>
       <c r="R51" t="n">
-        <v>6709628</v>
+        <v>6709660</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6205,7 +6129,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6215,7 +6139,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6242,10 +6166,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132439645</v>
+        <v>132439673</v>
       </c>
       <c r="B52" t="n">
-        <v>97995</v>
+        <v>8460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,34 +6177,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>551022</v>
+        <v>551162</v>
       </c>
       <c r="R52" t="n">
-        <v>6709604</v>
+        <v>6709731</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6312,7 +6241,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6322,7 +6251,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6349,10 +6278,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132439651</v>
+        <v>132439736</v>
       </c>
       <c r="B53" t="n">
-        <v>97995</v>
+        <v>8460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6360,34 +6289,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>551264</v>
+        <v>551353</v>
       </c>
       <c r="R53" t="n">
-        <v>6709457</v>
+        <v>6709650</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6419,7 +6353,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6429,7 +6363,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6456,10 +6390,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132439622</v>
+        <v>132439613</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6500,10 +6434,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>551221</v>
+        <v>550915</v>
       </c>
       <c r="R54" t="n">
-        <v>6709132</v>
+        <v>6709323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6535,7 +6469,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6545,7 +6479,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6572,42 +6506,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132439609</v>
+        <v>132439617</v>
       </c>
       <c r="B55" t="n">
-        <v>93206</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6616,10 +6550,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550993</v>
+        <v>551151</v>
       </c>
       <c r="R55" t="n">
-        <v>6709449</v>
+        <v>6709201</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6651,7 +6585,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6661,7 +6595,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6688,42 +6622,47 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132439611</v>
+        <v>132439620</v>
       </c>
       <c r="B56" t="n">
-        <v>93206</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6732,10 +6671,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550946</v>
+        <v>551210</v>
       </c>
       <c r="R56" t="n">
-        <v>6709448</v>
+        <v>6709145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,7 +6706,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6777,7 +6716,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6804,45 +6743,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132439644</v>
+        <v>132439622</v>
       </c>
       <c r="B57" t="n">
-        <v>79952</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>551030</v>
+        <v>551221</v>
       </c>
       <c r="R57" t="n">
-        <v>6709594</v>
+        <v>6709132</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6869,22 +6817,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6911,45 +6859,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132439679</v>
+        <v>132439626</v>
       </c>
       <c r="B58" t="n">
-        <v>79952</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>551266</v>
+        <v>551368</v>
       </c>
       <c r="R58" t="n">
-        <v>6709746</v>
+        <v>6709309</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6981,7 +6938,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6991,7 +6948,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7018,10 +6975,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132439629</v>
+        <v>132439627</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7062,10 +7019,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>551203</v>
+        <v>551369</v>
       </c>
       <c r="R59" t="n">
-        <v>6709203</v>
+        <v>6709297</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7097,7 +7054,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7107,7 +7064,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7134,45 +7091,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132439670</v>
+        <v>132439628</v>
       </c>
       <c r="B60" t="n">
-        <v>79952</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>551217</v>
+        <v>551318</v>
       </c>
       <c r="R60" t="n">
-        <v>6709702</v>
+        <v>6709291</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7204,7 +7170,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7214,7 +7180,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7241,45 +7207,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132439643</v>
+        <v>132439629</v>
       </c>
       <c r="B61" t="n">
-        <v>79952</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>551064</v>
+        <v>551203</v>
       </c>
       <c r="R61" t="n">
-        <v>6709434</v>
+        <v>6709203</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7311,7 +7286,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7321,7 +7296,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7348,45 +7323,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132439684</v>
+        <v>132439650</v>
       </c>
       <c r="B62" t="n">
-        <v>79952</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>551325</v>
+        <v>551247</v>
       </c>
       <c r="R62" t="n">
-        <v>6709728</v>
+        <v>6709492</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7418,7 +7402,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7428,7 +7412,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7455,45 +7439,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132439606</v>
+        <v>132439653</v>
       </c>
       <c r="B63" t="n">
-        <v>79952</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Trylämnet, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>551183</v>
+        <v>551344</v>
       </c>
       <c r="R63" t="n">
-        <v>6709426</v>
+        <v>6709420</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7520,22 +7513,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7559,6 +7552,1465 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132439654</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>551317</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6709485</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132439656</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>551280</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6709513</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132439657</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>551260</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6709510</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132439739</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>551352</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6709640</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132439740</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>551391</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6709619</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132439741</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>551384</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6709617</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132439742</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>551385</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6709617</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132439612</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>550898</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6709429</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132439616</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>551158</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6709205</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132439645</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>551022</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6709604</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132439651</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>551264</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6709457</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132439760</v>
+      </c>
+      <c r="B75" t="n">
+        <v>92188</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>551427</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6709469</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132439761</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Trylämnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>551427</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6709469</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8524-2026 artfynd.xlsx
+++ b/artfynd/A 8524-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439649</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439665</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439680</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439607</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439641</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439609</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439610</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439611</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439632</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1899,6 +1954,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439635</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2015,6 +2075,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439636</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439637</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439640</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2363,6 +2438,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439669</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2470,6 +2550,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439621</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2577,6 +2662,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439606</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2684,6 +2774,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439608</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2791,6 +2886,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439633</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2898,6 +2998,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439639</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3005,6 +3110,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439642</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3112,6 +3222,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439643</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3219,6 +3334,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439644</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3326,6 +3446,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3433,6 +3558,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439648</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3540,6 +3670,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439658</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3647,6 +3782,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439659</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3754,6 +3894,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439660</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3861,6 +4006,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439663</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3973,6 +4123,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439664</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4080,6 +4235,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439667</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4187,6 +4347,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439670</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4294,6 +4459,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439671</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4401,6 +4571,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439672</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4508,6 +4683,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439679</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4615,6 +4795,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439681</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4722,6 +4907,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439682</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4829,6 +5019,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439683</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4941,6 +5136,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439605</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5053,6 +5253,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439661</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5165,6 +5370,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439675</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5282,6 +5492,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439677</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5394,6 +5609,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445767</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5506,6 +5726,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439647</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5618,6 +5843,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439634</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5730,6 +5960,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439652</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5842,6 +6077,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439662</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5954,6 +6194,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439673</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6070,6 +6315,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439613</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6186,6 +6436,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439617</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6307,6 +6562,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439620</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6423,6 +6683,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439622</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6539,6 +6804,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439629</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6655,6 +6925,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439650</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6771,6 +7046,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439656</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6887,6 +7167,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439657</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6994,6 +7279,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439612</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7101,6 +7391,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439616</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7208,6 +7503,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439645</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7315,6 +7615,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439651</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7422,6 +7727,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439685</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7529,6 +7839,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439760</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7636,6 +7951,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439684</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7743,6 +8063,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439738</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7855,6 +8180,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439736</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7967,6 +8297,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439761</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8083,6 +8418,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439626</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8199,6 +8539,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439627</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8315,6 +8660,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439628</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8431,6 +8781,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439653</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8547,6 +8902,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439654</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8663,6 +9023,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439739</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8779,6 +9144,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439740</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8895,6 +9265,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439741</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9011,8 +9386,90 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132439742</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>